--- a/tiflow-core/telemetry-data-status-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/telemetry-data-status-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T13:24:36+00:00</t>
+    <t>2026-05-06T13:55:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/telemetry-data-status-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/telemetry-data-status-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T13:55:11+00:00</t>
+    <t>2026-05-06T14:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/telemetry-data-status-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow-core/telemetry-data-status-codes/1.0.0-draft/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T14:24:44+00:00</t>
+    <t>2026-05-06T14:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
